--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.91427775220145</v>
+        <v>3.561070134732736</v>
       </c>
       <c r="D2" t="n">
-        <v>22.59119197619501</v>
+        <v>3.671068696131689</v>
       </c>
       <c r="E2" t="n">
-        <v>14.11927344391112</v>
+        <v>2.294381934635557</v>
       </c>
       <c r="F2" t="n">
-        <v>12.997498174337</v>
+        <v>2.112093453329762</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.71453856724959</v>
+        <v>5.478612517178059</v>
       </c>
       <c r="D3" t="n">
-        <v>19.31310125013452</v>
+        <v>3.13837895314686</v>
       </c>
       <c r="E3" t="n">
-        <v>14.11927344391112</v>
+        <v>2.294381934635557</v>
       </c>
       <c r="F3" t="n">
-        <v>12.997498174337</v>
+        <v>2.112093453329762</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.2570848175281</v>
+        <v>3.454276282848316</v>
       </c>
       <c r="D4" t="n">
-        <v>25.48997489802182</v>
+        <v>4.142120920928547</v>
       </c>
       <c r="E4" t="n">
-        <v>14.11927344391112</v>
+        <v>2.294381934635557</v>
       </c>
       <c r="F4" t="n">
-        <v>12.997498174337</v>
+        <v>2.112093453329762</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.16007746189351</v>
+        <v>9.126012587557696</v>
       </c>
       <c r="D5" t="n">
-        <v>52.05392009561506</v>
+        <v>8.458762015537447</v>
       </c>
       <c r="E5" t="n">
-        <v>14.11927344391112</v>
+        <v>2.294381934635557</v>
       </c>
       <c r="F5" t="n">
-        <v>12.997498174337</v>
+        <v>2.112093453329762</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
